--- a/Datas/Map.xlsx
+++ b/Datas/Map.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="17535" windowHeight="8220"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -181,7 +181,7 @@
     <t>寒冷雪山，珍奇动物</t>
   </si>
   <si>
-    <t>Arts/UI/Prepare/Map_Mountain</t>
+    <t>Arts/UI/Prepare/Map_SnowMountain</t>
   </si>
   <si>
     <t xml:space="preserve">隐藏地图 </t>

--- a/Datas/Map.xlsx
+++ b/Datas/Map.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="17535" windowHeight="8220"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Datas/Map.xlsx
+++ b/Datas/Map.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="16245" windowHeight="5985"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -121,7 +121,7 @@
     <t>Small:101,0.6;102,0.4|Medium:201,0.34;202,0.33;203,0.33|Large:301,1|Special:401,0.8;402,0.2</t>
   </si>
   <si>
-    <t>Arts/UI/Prepare/Map_Forest</t>
+    <t>Arts/UI/Prepare/TB_beijing_0001</t>
   </si>
   <si>
     <t xml:space="preserve">紫薇主场地图 </t>
@@ -136,7 +136,7 @@
     <t>阳光沙滩，海洋生物</t>
   </si>
   <si>
-    <t>Arts/UI/Prepare/Map_Beach</t>
+    <t>Arts/UI/Prepare/TB_beijing_0002</t>
   </si>
   <si>
     <t xml:space="preserve">大美丽主场地图 </t>
@@ -151,7 +151,7 @@
     <t>精致花园，稀有物种</t>
   </si>
   <si>
-    <t>Arts/UI/Prepare/Map_Garden</t>
+    <t>Arts/UI/Prepare/TB_beijing_0003</t>
   </si>
   <si>
     <t xml:space="preserve">金状元主场地图 </t>
@@ -166,7 +166,7 @@
     <t>广袤的草原，适合狩猎</t>
   </si>
   <si>
-    <t>Arts/UI/Prepare/Map_Grassland</t>
+    <t>Arts/UI/Prepare/TB_beijing_0004</t>
   </si>
   <si>
     <t xml:space="preserve">亚克东主场地图 </t>
@@ -181,7 +181,7 @@
     <t>寒冷雪山，珍奇动物</t>
   </si>
   <si>
-    <t>Arts/UI/Prepare/Map_SnowMountain</t>
+    <t>Arts/UI/Prepare/TB_beijing_0005</t>
   </si>
   <si>
     <t xml:space="preserve">隐藏地图 </t>

--- a/Datas/Map.xlsx
+++ b/Datas/Map.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="16245" windowHeight="5985"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Datas/Map.xlsx
+++ b/Datas/Map.xlsx
@@ -172,7 +172,7 @@
     <t xml:space="preserve">亚克东主场地图 </t>
   </si>
   <si>
-    <t>Mountain</t>
+    <t>Hidden</t>
   </si>
   <si>
     <t>远古雪山</t>
@@ -1160,7 +1160,8 @@
     <col min="1" max="5" width="28.625" customWidth="1"/>
     <col min="6" max="6" width="28" customWidth="1"/>
     <col min="7" max="7" width="114.283333333333" customWidth="1"/>
-    <col min="8" max="9" width="28.625" customWidth="1"/>
+    <col min="8" max="8" width="56.625" customWidth="1"/>
+    <col min="9" max="9" width="28.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:9">

--- a/Datas/Map.xlsx
+++ b/Datas/Map.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="53">
   <si>
     <t>##var</t>
   </si>
@@ -118,22 +118,25 @@
     <t>1</t>
   </si>
   <si>
+    <t>Small:101,0.6;102,0.4|Medium:201,0.34;202,0.33;203,0.33|Large:301,1|Special:401,0.5;402,05</t>
+  </si>
+  <si>
+    <t>Arts/UI/Prepare/TB_beijing_0001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">紫薇主场地图 </t>
+  </si>
+  <si>
+    <t>Beach</t>
+  </si>
+  <si>
+    <t>海滨沙滩度假村</t>
+  </si>
+  <si>
+    <t>阳光沙滩，海洋生物</t>
+  </si>
+  <si>
     <t>Small:101,0.6;102,0.4|Medium:201,0.34;202,0.33;203,0.33|Large:301,1|Special:401,0.8;402,0.2</t>
-  </si>
-  <si>
-    <t>Arts/UI/Prepare/TB_beijing_0001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">紫薇主场地图 </t>
-  </si>
-  <si>
-    <t>Beach</t>
-  </si>
-  <si>
-    <t>海滨沙滩度假村</t>
-  </si>
-  <si>
-    <t>阳光沙滩，海洋生物</t>
   </si>
   <si>
     <t>Arts/UI/Prepare/TB_beijing_0002</t>
@@ -1325,13 +1328,13 @@
         <v>28</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:9">
@@ -1340,25 +1343,25 @@
         <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>28</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:9">
@@ -1367,25 +1370,25 @@
         <v>4</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>28</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:9">
@@ -1394,25 +1397,25 @@
         <v>5</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>28</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/Map.xlsx
+++ b/Datas/Map.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="58">
   <si>
     <t>##var</t>
   </si>
@@ -46,10 +46,10 @@
     <t>Description</t>
   </si>
   <si>
-    <t>SpawnStrategyId</t>
-  </si>
-  <si>
-    <t>SpeciesByVolume</t>
+    <t>SpecieTypeWeights</t>
+  </si>
+  <si>
+    <t>MapSpecies</t>
   </si>
   <si>
     <t>MapImageResourcePath</t>
@@ -70,7 +70,10 @@
     <t>string</t>
   </si>
   <si>
-    <t>(map#sep=:|),HuntingConfig.Enum.EVolumeType,(array#sep=;),HuntingConfig.Bean.SpecieWeight</t>
+    <t>(map#sep=:|),HuntingConfig.Enum.ESpecieType,float</t>
+  </si>
+  <si>
+    <t>(map#sep=:|),HuntingConfig.Enum.ESpecieType,(array#sep=,),int</t>
   </si>
   <si>
     <t>##group</t>
@@ -94,10 +97,10 @@
     <t>地图描述</t>
   </si>
   <si>
-    <t>体型策略ID</t>
-  </si>
-  <si>
-    <t>体型-物种权重映射</t>
+    <t>物种类型权重</t>
+  </si>
+  <si>
+    <t>地图物种</t>
   </si>
   <si>
     <t>地图图片资源路径</t>
@@ -112,13 +115,13 @@
     <t>皇家猎场森林</t>
   </si>
   <si>
-    <t>茂密森林，神秘动物</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>Small:101,0.6;102,0.4|Medium:201,0.34;202,0.33;203,0.33|Large:301,1|Special:401,0.5;402,05</t>
+    <t>茂密的皇家猎场森林</t>
+  </si>
+  <si>
+    <t>Small:50|Medium:30|Large:10|Bullet:8|ThreeKPCoin:2</t>
+  </si>
+  <si>
+    <t>Small:101,102|Medium:201,202,203|Large:301|Bullet:401|ThreeKPCoin:402</t>
   </si>
   <si>
     <t>Arts/UI/Prepare/TB_beijing_0001</t>
@@ -133,10 +136,10 @@
     <t>海滨沙滩度假村</t>
   </si>
   <si>
-    <t>阳光沙滩，海洋生物</t>
-  </si>
-  <si>
-    <t>Small:101,0.6;102,0.4|Medium:201,0.34;202,0.33;203,0.33|Large:301,1|Special:401,0.8;402,0.2</t>
+    <t>美丽的海滨沙滩度假村</t>
+  </si>
+  <si>
+    <t>Small:103,104|Medium:204,205,206|Large:302|Bullet:401|ThreeKPCoin:402</t>
   </si>
   <si>
     <t>Arts/UI/Prepare/TB_beijing_0002</t>
@@ -151,7 +154,10 @@
     <t>金状元私家花园</t>
   </si>
   <si>
-    <t>精致花园，稀有物种</t>
+    <t>幽静的金状元私家花园</t>
+  </si>
+  <si>
+    <t>Small:105,106|Medium:207,208,209|Large:303|Bullet:401|ThreeKPCoin:402</t>
   </si>
   <si>
     <t>Arts/UI/Prepare/TB_beijing_0003</t>
@@ -166,7 +172,10 @@
     <t>新疆大草原</t>
   </si>
   <si>
-    <t>广袤的草原，适合狩猎</t>
+    <t>广阔的新疆大草原</t>
+  </si>
+  <si>
+    <t>Small:107,108|Medium:210,211,212|Large:304|Bullet:401|ThreeKPCoin:402</t>
   </si>
   <si>
     <t>Arts/UI/Prepare/TB_beijing_0004</t>
@@ -181,7 +190,13 @@
     <t>远古雪山</t>
   </si>
   <si>
-    <t>寒冷雪山，珍奇动物</t>
+    <t>神秘的远古雪山</t>
+  </si>
+  <si>
+    <t>Small:95|Bullet:5</t>
+  </si>
+  <si>
+    <t>Small:109,110|Bullet:401</t>
   </si>
   <si>
     <t>Arts/UI/Prepare/TB_beijing_0005</t>
@@ -1160,10 +1175,12 @@
   <dimension ref="A1:I9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="5" width="28.625" customWidth="1"/>
-    <col min="6" max="6" width="28" customWidth="1"/>
-    <col min="7" max="7" width="114.283333333333" customWidth="1"/>
-    <col min="8" max="8" width="56.625" customWidth="1"/>
+    <col min="1" max="2" width="28.625" customWidth="1"/>
+    <col min="3" max="3" width="48.625" customWidth="1"/>
+    <col min="4" max="5" width="28.625" customWidth="1"/>
+    <col min="6" max="6" width="56.625" customWidth="1"/>
+    <col min="7" max="7" width="96.625" customWidth="1"/>
+    <col min="8" max="8" width="48.625" customWidth="1"/>
     <col min="9" max="9" width="28.625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1213,10 +1230,10 @@
         <v>12</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>12</v>
@@ -1227,60 +1244,60 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:9">
@@ -1289,25 +1306,25 @@
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:9">
@@ -1316,25 +1333,25 @@
         <v>2</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:9">
@@ -1343,25 +1360,25 @@
         <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:9">
@@ -1370,25 +1387,25 @@
         <v>4</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:9">
@@ -1397,25 +1414,25 @@
         <v>5</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/Map.xlsx
+++ b/Datas/Map.xlsx
@@ -196,7 +196,7 @@
     <t>Small:95|Bullet:5</t>
   </si>
   <si>
-    <t>Small:109,110|Bullet:401</t>
+    <t>Small:109,110|Bullet:401|Boss:501,502,503,504</t>
   </si>
   <si>
     <t>Arts/UI/Prepare/TB_beijing_0005</t>

--- a/Datas/Map.xlsx
+++ b/Datas/Map.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -124,7 +124,7 @@
     <t>Small:101,102|Medium:201,202,203|Large:301|Bullet:401|ThreeKPCoin:402</t>
   </si>
   <si>
-    <t>Arts/UI/Prepare/TB_beijing_0001</t>
+    <t>Assets/Arts/UI/Sprites/Prepare/Maps/TB_beijing_0001</t>
   </si>
   <si>
     <t xml:space="preserve">紫薇主场地图 </t>
@@ -142,7 +142,7 @@
     <t>Small:103,104|Medium:204,205,206|Large:302|Bullet:401|ThreeKPCoin:402</t>
   </si>
   <si>
-    <t>Arts/UI/Prepare/TB_beijing_0002</t>
+    <t>Assets/Arts/UI/Sprites/Prepare/Maps/TB_beijing_0002</t>
   </si>
   <si>
     <t xml:space="preserve">大美丽主场地图 </t>
@@ -160,7 +160,7 @@
     <t>Small:105,106|Medium:207,208,209|Large:303|Bullet:401|ThreeKPCoin:402</t>
   </si>
   <si>
-    <t>Arts/UI/Prepare/TB_beijing_0003</t>
+    <t>Assets/Arts/UI/Sprites/Prepare/Maps/TB_beijing_0003</t>
   </si>
   <si>
     <t xml:space="preserve">金状元主场地图 </t>
@@ -178,7 +178,7 @@
     <t>Small:107,108|Medium:210,211,212|Large:304|Bullet:401|ThreeKPCoin:402</t>
   </si>
   <si>
-    <t>Arts/UI/Prepare/TB_beijing_0004</t>
+    <t>Assets/Arts/UI/Sprites/Prepare/Maps/TB_beijing_0004</t>
   </si>
   <si>
     <t xml:space="preserve">亚克东主场地图 </t>
@@ -199,7 +199,7 @@
     <t>Small:109,110|Bullet:401|Boss:501,502,503,504</t>
   </si>
   <si>
-    <t>Arts/UI/Prepare/TB_beijing_0005</t>
+    <t>Assets/Arts/UI/Sprites/Prepare/Maps/TB_beijing_0005</t>
   </si>
   <si>
     <t xml:space="preserve">隐藏地图 </t>

--- a/Datas/Map.xlsx
+++ b/Datas/Map.xlsx
@@ -118,7 +118,7 @@
     <t>茂密的皇家猎场森林</t>
   </si>
   <si>
-    <t>Small:50|Medium:30|Large:10|Bullet:8|ThreeKPCoin:2</t>
+    <t>Small:50|Medium:30|Large:10|Bullet:3|ThreeKPCoin:3</t>
   </si>
   <si>
     <t>Small:101,102|Medium:201,202,203|Large:301|Bullet:401|ThreeKPCoin:402</t>
@@ -193,7 +193,7 @@
     <t>神秘的远古雪山</t>
   </si>
   <si>
-    <t>Small:95|Bullet:5</t>
+    <t>Small:90|Bullet:10</t>
   </si>
   <si>
     <t>Small:109,110|Bullet:401|Boss:501,502,503,504</t>

--- a/Datas/Map.xlsx
+++ b/Datas/Map.xlsx
@@ -196,7 +196,7 @@
     <t>Small:90|Bullet:10</t>
   </si>
   <si>
-    <t>Small:109,110|Bullet:401|Boss:501,502,503,504</t>
+    <t>Small:109|Bullet:401|Boss:501,502,503,504</t>
   </si>
   <si>
     <t>Assets/Arts/UI/Sprites/Prepare/Maps/TB_beijing_0005</t>

--- a/Datas/Map.xlsx
+++ b/Datas/Map.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -196,7 +196,7 @@
     <t>Small:90|Bullet:10</t>
   </si>
   <si>
-    <t>Small:109|Bullet:401|Boss:501,502,503,504</t>
+    <t>Small:109,110|Bullet:401|Boss:501,502,503,504</t>
   </si>
   <si>
     <t>Assets/Arts/UI/Sprites/Prepare/Maps/TB_beijing_0005</t>

--- a/Datas/Map.xlsx
+++ b/Datas/Map.xlsx
@@ -124,7 +124,7 @@
     <t>Small:101,102|Medium:201,202,203|Large:301|Bullet:401|ThreeKPCoin:402</t>
   </si>
   <si>
-    <t>Assets/Arts/UI/Sprites/Prepare/Maps/TB_beijing_0001</t>
+    <t>Assets/Arts/UI/Sprites/Prepare/Main/Maps/TB_beijing_0001</t>
   </si>
   <si>
     <t xml:space="preserve">紫薇主场地图 </t>
@@ -142,7 +142,7 @@
     <t>Small:103,104|Medium:204,205,206|Large:302|Bullet:401|ThreeKPCoin:402</t>
   </si>
   <si>
-    <t>Assets/Arts/UI/Sprites/Prepare/Maps/TB_beijing_0002</t>
+    <t>Assets/Arts/UI/Sprites/Prepare/Main/Maps/TB_beijing_0002</t>
   </si>
   <si>
     <t xml:space="preserve">大美丽主场地图 </t>
@@ -160,7 +160,7 @@
     <t>Small:105,106|Medium:207,208,209|Large:303|Bullet:401|ThreeKPCoin:402</t>
   </si>
   <si>
-    <t>Assets/Arts/UI/Sprites/Prepare/Maps/TB_beijing_0003</t>
+    <t>Assets/Arts/UI/Sprites/Prepare/Main/Maps/TB_beijing_0003</t>
   </si>
   <si>
     <t xml:space="preserve">金状元主场地图 </t>
@@ -178,7 +178,7 @@
     <t>Small:107,108|Medium:210,211,212|Large:304|Bullet:401|ThreeKPCoin:402</t>
   </si>
   <si>
-    <t>Assets/Arts/UI/Sprites/Prepare/Maps/TB_beijing_0004</t>
+    <t>Assets/Arts/UI/Sprites/Prepare/Main/Maps/TB_beijing_0004</t>
   </si>
   <si>
     <t xml:space="preserve">亚克东主场地图 </t>
@@ -199,7 +199,7 @@
     <t>Small:109,110|Bullet:401|Boss:501,502,503,504</t>
   </si>
   <si>
-    <t>Assets/Arts/UI/Sprites/Prepare/Maps/TB_beijing_0005</t>
+    <t>Assets/Arts/UI/Sprites/Prepare/Main/Maps/TB_beijing_0005</t>
   </si>
   <si>
     <t xml:space="preserve">隐藏地图 </t>

--- a/Datas/Map.xlsx
+++ b/Datas/Map.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="53">
   <si>
     <t>##var</t>
   </si>
@@ -115,9 +115,6 @@
     <t>皇家猎场森林</t>
   </si>
   <si>
-    <t>茂密的皇家猎场森林</t>
-  </si>
-  <si>
     <t>Small:50|Medium:30|Large:10|Bullet:3|ThreeKPCoin:3</t>
   </si>
   <si>
@@ -136,9 +133,6 @@
     <t>海滨沙滩度假村</t>
   </si>
   <si>
-    <t>美丽的海滨沙滩度假村</t>
-  </si>
-  <si>
     <t>Small:103,104|Medium:204,205,206|Large:302|Bullet:401|ThreeKPCoin:402</t>
   </si>
   <si>
@@ -154,9 +148,6 @@
     <t>金状元私家花园</t>
   </si>
   <si>
-    <t>幽静的金状元私家花园</t>
-  </si>
-  <si>
     <t>Small:105,106|Medium:207,208,209|Large:303|Bullet:401|ThreeKPCoin:402</t>
   </si>
   <si>
@@ -169,10 +160,7 @@
     <t>Grassland</t>
   </si>
   <si>
-    <t>新疆大草原</t>
-  </si>
-  <si>
-    <t>广阔的新疆大草原</t>
+    <t>西域大草原</t>
   </si>
   <si>
     <t>Small:107,108|Medium:210,211,212|Large:304|Bullet:401|ThreeKPCoin:402</t>
@@ -188,9 +176,6 @@
   </si>
   <si>
     <t>远古雪山</t>
-  </si>
-  <si>
-    <t>神秘的远古雪山</t>
   </si>
   <si>
     <t>Small:90|Bullet:10</t>
@@ -1176,11 +1161,12 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="28.625" customWidth="1"/>
-    <col min="3" max="3" width="48.625" customWidth="1"/>
-    <col min="4" max="5" width="28.625" customWidth="1"/>
+    <col min="3" max="3" width="36.625" customWidth="1"/>
+    <col min="4" max="4" width="28.625" customWidth="1"/>
+    <col min="5" max="5" width="48.625" customWidth="1"/>
     <col min="6" max="6" width="56.625" customWidth="1"/>
     <col min="7" max="7" width="96.625" customWidth="1"/>
-    <col min="8" max="8" width="48.625" customWidth="1"/>
+    <col min="8" max="8" width="76.625" customWidth="1"/>
     <col min="9" max="9" width="28.625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1312,19 +1298,19 @@
         <v>27</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="H5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:9">
@@ -1333,25 +1319,25 @@
         <v>2</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="H6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="I6" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:9">
@@ -1360,25 +1346,25 @@
         <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="H7" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="I7" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:9">
@@ -1387,25 +1373,25 @@
         <v>4</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="I8" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:9">
@@ -1414,25 +1400,25 @@
         <v>5</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="I9" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/Map.xlsx
+++ b/Datas/Map.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="34">
   <si>
     <t>##var</t>
   </si>
@@ -52,9 +52,6 @@
     <t>MapSpecies</t>
   </si>
   <si>
-    <t>MapImageResourcePath</t>
-  </si>
-  <si>
     <t>Comment</t>
   </si>
   <si>
@@ -103,9 +100,6 @@
     <t>地图物种</t>
   </si>
   <si>
-    <t>地图图片资源路径</t>
-  </si>
-  <si>
     <t>备注</t>
   </si>
   <si>
@@ -115,76 +109,25 @@
     <t>皇家猎场森林</t>
   </si>
   <si>
-    <t>Small:50|Medium:30|Large:10|Bullet:3|ThreeKPCoin:3</t>
-  </si>
-  <si>
-    <t>Small:101,102|Medium:201,202,203|Large:301|Bullet:401|ThreeKPCoin:402</t>
-  </si>
-  <si>
-    <t>Assets/Arts/UI/Sprites/Prepare/Main/Maps/TB_beijing_0001</t>
+    <t>Small:50|Medium:30|Large:10|Bullet:2|ThreeKPCoin:2</t>
+  </si>
+  <si>
+    <t>Small:101,102|Medium:201,202|Large:301,302|Bullet:401|ThreeKPCoin:402</t>
   </si>
   <si>
     <t xml:space="preserve">紫薇主场地图 </t>
   </si>
   <si>
-    <t>Beach</t>
-  </si>
-  <si>
-    <t>海滨沙滩度假村</t>
-  </si>
-  <si>
-    <t>Small:103,104|Medium:204,205,206|Large:302|Bullet:401|ThreeKPCoin:402</t>
-  </si>
-  <si>
-    <t>Assets/Arts/UI/Sprites/Prepare/Main/Maps/TB_beijing_0002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">大美丽主场地图 </t>
-  </si>
-  <si>
-    <t>Garden</t>
-  </si>
-  <si>
-    <t>金状元私家花园</t>
-  </si>
-  <si>
-    <t>Small:105,106|Medium:207,208,209|Large:303|Bullet:401|ThreeKPCoin:402</t>
-  </si>
-  <si>
-    <t>Assets/Arts/UI/Sprites/Prepare/Main/Maps/TB_beijing_0003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">金状元主场地图 </t>
-  </si>
-  <si>
-    <t>Grassland</t>
-  </si>
-  <si>
-    <t>西域大草原</t>
-  </si>
-  <si>
-    <t>Small:107,108|Medium:210,211,212|Large:304|Bullet:401|ThreeKPCoin:402</t>
-  </si>
-  <si>
-    <t>Assets/Arts/UI/Sprites/Prepare/Main/Maps/TB_beijing_0004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">亚克东主场地图 </t>
-  </si>
-  <si>
     <t>Hidden</t>
   </si>
   <si>
     <t>远古雪山</t>
   </si>
   <si>
-    <t>Small:90|Bullet:10</t>
+    <t>Small:90|Bullet:5</t>
   </si>
   <si>
     <t>Small:109,110|Bullet:401|Boss:501,502,503,504</t>
-  </si>
-  <si>
-    <t>Assets/Arts/UI/Sprites/Prepare/Main/Maps/TB_beijing_0005</t>
   </si>
   <si>
     <t xml:space="preserve">隐藏地图 </t>
@@ -1157,20 +1100,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="28.625" customWidth="1"/>
     <col min="3" max="3" width="36.625" customWidth="1"/>
     <col min="4" max="4" width="28.625" customWidth="1"/>
     <col min="5" max="5" width="48.625" customWidth="1"/>
-    <col min="6" max="6" width="56.625" customWidth="1"/>
-    <col min="7" max="7" width="96.625" customWidth="1"/>
-    <col min="8" max="8" width="76.625" customWidth="1"/>
-    <col min="9" max="9" width="28.625" customWidth="1"/>
+    <col min="6" max="6" width="64.625" customWidth="1"/>
+    <col min="7" max="7" width="76.625" customWidth="1"/>
+    <col min="8" max="8" width="28.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:9">
+    <row r="1" ht="28" customHeight="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1195,230 +1137,131 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+    </row>
+    <row r="2" ht="28" customHeight="1" spans="1:8">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:9">
-      <c r="A2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="1" t="s">
+    <row r="3" ht="28" customHeight="1" spans="1:8">
+      <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>12</v>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1" spans="1:9">
-      <c r="A3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="4" ht="28" customHeight="1" spans="1:8">
+      <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>16</v>
+      <c r="B4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1" spans="1:9">
-      <c r="A4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="1:9">
+    <row r="5" ht="28" customHeight="1" spans="1:8">
       <c r="A5" s="2"/>
       <c r="B5" s="2">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="G5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="4" t="s">
+      <c r="H5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>31</v>
-      </c>
     </row>
-    <row r="6" ht="28" customHeight="1" spans="1:9">
+    <row r="6" ht="28" customHeight="1" spans="1:8">
       <c r="A6" s="2"/>
       <c r="B6" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="H6" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1" spans="1:9">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2">
-        <v>3</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1" spans="1:9">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2">
-        <v>4</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1" spans="1:9">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2">
-        <v>5</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/Map.xlsx
+++ b/Datas/Map.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="32">
   <si>
     <t>##var</t>
   </si>
@@ -52,9 +52,6 @@
     <t>MapSpecies</t>
   </si>
   <si>
-    <t>Comment</t>
-  </si>
-  <si>
     <t>##type</t>
   </si>
   <si>
@@ -100,37 +97,34 @@
     <t>地图物种</t>
   </si>
   <si>
-    <t>备注</t>
-  </si>
-  <si>
     <t>Forest</t>
   </si>
   <si>
     <t>皇家猎场森林</t>
   </si>
   <si>
-    <t>Small:50|Medium:30|Large:10|Bullet:2|ThreeKPCoin:2</t>
+    <t>格格最喜欢陪阿玛来这里打猎</t>
+  </si>
+  <si>
+    <t>Small:45|Medium:30|Large:10|Bullet:3|ThreeKPCoin:3</t>
   </si>
   <si>
     <t>Small:101,102|Medium:201,202|Large:301,302|Bullet:401|ThreeKPCoin:402</t>
   </si>
   <si>
-    <t xml:space="preserve">紫薇主场地图 </t>
-  </si>
-  <si>
     <t>Hidden</t>
   </si>
   <si>
     <t>远古雪山</t>
   </si>
   <si>
-    <t>Small:90|Bullet:5</t>
+    <t>动人的远古雪山</t>
+  </si>
+  <si>
+    <t>Small:90|Bullet:10</t>
   </si>
   <si>
     <t>Small:109,110|Bullet:401|Boss:501,502,503,504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">隐藏地图 </t>
   </si>
 </sst>
 </file>
@@ -1100,8 +1094,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="7"/>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="2" width="28.625" customWidth="1"/>
     <col min="3" max="3" width="36.625" customWidth="1"/>
@@ -1109,10 +1103,9 @@
     <col min="5" max="5" width="48.625" customWidth="1"/>
     <col min="6" max="6" width="64.625" customWidth="1"/>
     <col min="7" max="7" width="76.625" customWidth="1"/>
-    <col min="8" max="8" width="28.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:8">
+    <row r="1" ht="28" customHeight="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1134,134 +1127,116 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+    </row>
+    <row r="2" ht="28" customHeight="1" spans="1:7">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:8">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="1" t="s">
+    <row r="3" ht="28" customHeight="1" spans="1:7">
+      <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>11</v>
+      <c r="B3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1" spans="1:8">
-      <c r="A3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="4" ht="28" customHeight="1" spans="1:7">
+      <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>15</v>
+      <c r="B4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1" spans="1:8">
-      <c r="A4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="1:8">
+    <row r="5" ht="28" customHeight="1" spans="1:7">
       <c r="A5" s="2"/>
       <c r="B5" s="2">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>28</v>
-      </c>
     </row>
-    <row r="6" ht="28" customHeight="1" spans="1:8">
+    <row r="6" ht="28" customHeight="1" spans="1:7">
       <c r="A6" s="2"/>
       <c r="B6" s="2">
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="F6" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>33</v>
       </c>
     </row>
   </sheetData>
